--- a/result.xlsx
+++ b/result.xlsx
@@ -6,31 +6,31 @@
     <sheet state="visible" name="5th" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_306D586A_A5AC_4229_9E1C_5457B85CC7A8_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_7356B801_1C63_4121_8D46_7701FF85BCCF_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_85EBEFAE_B28A_4127_B6B4_6AC4CCC8C134_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_855D6783_E89F_4AEB_97D0_945807C7153F_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_BA280C03_A6D0_4DDC_8248_3342070E140F_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_6A080B14_C65B_46DD_97E6_498C19CD9206_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_0367D160_10D3_45F3_A48E_CCB1E25EADB5_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_CCFC2D6D_1682_4A8C_B48A_667DB9857DDD_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_3A2C5092_5A3C_4B76_8D10_65234E69162B_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_6C1217AC_2F5B_4B9C_9906_85A2A50A1B7D_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_AAFBD7D5_478E_4F1A_B903_212B193B56E9_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_ECF78DD8_3C13_45CB_A702_9BDF29315AF0_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_8AACF8F8_B55E_4915_9F46_991C008EBE09_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_B42CC50D_F60F_42F9_B8C0_FC77153034DE_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_6EA19BB9_567C_4055_96CB_2C19019C8916_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_1EA62444_B123_4C0B_8F7F_3B200448A206_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_BDCCA16F_5B03_4638_AFE1_84255B44CB7F_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_6CFFF1F8_EEAD_47B1_A5BA_9B98655A952B_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_42D6E9FA_5371_4DCF_B97C_438E291F0C15_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_D6D6AAF0_767B_47ED_B3D3_B6430EEAFC24_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_E19D6905_7219_4716_8E35_399AC7C1BC00_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_1B3A8ACD_D417_4637_A685_81D9381FF1DE_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{855D6783-E89F-4AEB-97D0-945807C7153F}" name="Group by School Name [2]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{6A080B14-C65B-46DD-97E6-498C19CD9206}" name="Group by School Name [3]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{CCFC2D6D-1682-4A8C-B48A-667DB9857DDD}" name="Group by School Name [6]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{3A2C5092-5A3C-4B76-8D10-65234E69162B}" name="Group by School Name [7]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{85EBEFAE-B28A-4127-B6B4-6AC4CCC8C134}" name="Group by School Name [4]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{6C1217AC-2F5B-4B9C-9906-85A2A50A1B7D}" name="Group by School Name [5]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{306D586A-A5AC-4229-9E1C-5457B85CC7A8}" name="Group by School Name [8]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{AAFBD7D5-478E-4F1A-B903-212B193B56E9}" name="Group by Class"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{7356B801-1C63-4121-8D46-7701FF85BCCF}" name="Group by Class [3]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{0367D160-10D3-45F3-A48E-CCB1E25EADB5}" name="Group by Class [2]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{BA280C03-A6D0-4DDC-8248-3342070E140F}" name="Group by School Name"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{8AACF8F8-B55E-4915-9F46-991C008EBE09}" name="Group by School Name [2]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{6EA19BB9-567C-4055-96CB-2C19019C8916}" name="Group by School Name [3]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ECF78DD8-3C13-45CB-A702-9BDF29315AF0}" name="Group by School Name [6]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{B42CC50D-F60F-42F9-B8C0-FC77153034DE}" name="Group by School Name [7]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{E19D6905-7219-4716-8E35-399AC7C1BC00}" name="Group by School Name [4]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{42D6E9FA-5371-4DCF-B97C-438E291F0C15}" name="Group by School Name [5]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{1EA62444-B123-4C0B-8F7F-3B200448A206}" name="Group by School Name [8]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{BDCCA16F-5B03-4638-AFE1-84255B44CB7F}" name="Group by Class"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{1B3A8ACD-D417-4637-A685-81D9381FF1DE}" name="Group by Class [3]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{D6D6AAF0-767B-47ED-B3D3-B6430EEAFC24}" name="Group by Class [2]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{6CFFF1F8-EEAD-47B1-A5BA-9B98655A952B}" name="Group by School Name"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -2018,7 +2018,7 @@
     <t>FAP26-EAE-08-08</t>
   </si>
   <si>
-    <t>MD.SAZIT</t>
+    <t>MD. SAZID</t>
   </si>
   <si>
     <t>MD. CHHOTE</t>
@@ -3784,7 +3784,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3850,6 +3850,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -4179,6 +4182,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -11146,7 +11150,7 @@
       <c r="B168" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="C168" s="12" t="s">
+      <c r="C168" s="24" t="s">
         <v>660</v>
       </c>
       <c r="D168" s="12" t="s">
@@ -17724,574 +17728,577 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="24"/>
-      <c r="B325" s="24"/>
-      <c r="C325" s="24"/>
-      <c r="D325" s="24"/>
-      <c r="E325" s="24"/>
-      <c r="F325" s="24"/>
-      <c r="G325" s="24"/>
-      <c r="H325" s="25"/>
-      <c r="I325" s="25"/>
-      <c r="J325" s="25"/>
-      <c r="K325" s="25"/>
-      <c r="L325" s="25"/>
-      <c r="M325" s="25"/>
+      <c r="A325" s="25"/>
+      <c r="B325" s="25"/>
+      <c r="C325" s="25"/>
+      <c r="D325" s="25"/>
+      <c r="E325" s="25"/>
+      <c r="F325" s="25"/>
+      <c r="G325" s="25"/>
+      <c r="H325" s="26"/>
+      <c r="I325" s="26"/>
+      <c r="J325" s="26"/>
+      <c r="K325" s="26"/>
+      <c r="L325" s="26"/>
+      <c r="M325" s="26"/>
     </row>
     <row r="326">
-      <c r="A326" s="24"/>
-      <c r="B326" s="24"/>
-      <c r="C326" s="24"/>
-      <c r="D326" s="24"/>
-      <c r="E326" s="24"/>
-      <c r="F326" s="24"/>
-      <c r="G326" s="24"/>
-      <c r="H326" s="25"/>
-      <c r="I326" s="25"/>
-      <c r="J326" s="25"/>
-      <c r="K326" s="25"/>
-      <c r="L326" s="25"/>
-      <c r="M326" s="25"/>
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+      <c r="D326" s="25"/>
+      <c r="E326" s="25"/>
+      <c r="F326" s="25"/>
+      <c r="G326" s="25"/>
+      <c r="H326" s="26"/>
+      <c r="I326" s="26"/>
+      <c r="J326" s="26"/>
+      <c r="K326" s="26"/>
+      <c r="L326" s="26"/>
+      <c r="M326" s="26"/>
     </row>
     <row r="327">
-      <c r="A327" s="24"/>
-      <c r="B327" s="24"/>
-      <c r="C327" s="24"/>
-      <c r="D327" s="24"/>
-      <c r="E327" s="24"/>
-      <c r="F327" s="24"/>
-      <c r="G327" s="24"/>
-      <c r="H327" s="25"/>
-      <c r="I327" s="25"/>
-      <c r="J327" s="25"/>
-      <c r="K327" s="25"/>
-      <c r="L327" s="25"/>
-      <c r="M327" s="25"/>
+      <c r="A327" s="25"/>
+      <c r="B327" s="25"/>
+      <c r="C327" s="25"/>
+      <c r="D327" s="25"/>
+      <c r="E327" s="25"/>
+      <c r="F327" s="25"/>
+      <c r="G327" s="25"/>
+      <c r="H327" s="26"/>
+      <c r="I327" s="26"/>
+      <c r="J327" s="26"/>
+      <c r="K327" s="26"/>
+      <c r="L327" s="26"/>
+      <c r="M327" s="26"/>
     </row>
     <row r="328">
-      <c r="A328" s="24"/>
-      <c r="B328" s="24"/>
-      <c r="C328" s="24"/>
-      <c r="D328" s="24"/>
-      <c r="E328" s="24"/>
-      <c r="F328" s="24"/>
-      <c r="G328" s="24"/>
-      <c r="H328" s="25"/>
-      <c r="I328" s="25"/>
-      <c r="J328" s="25"/>
-      <c r="K328" s="25"/>
-      <c r="L328" s="25"/>
-      <c r="M328" s="25"/>
+      <c r="A328" s="25"/>
+      <c r="B328" s="25"/>
+      <c r="C328" s="25"/>
+      <c r="D328" s="25"/>
+      <c r="E328" s="25"/>
+      <c r="F328" s="25"/>
+      <c r="G328" s="25"/>
+      <c r="H328" s="26"/>
+      <c r="I328" s="26"/>
+      <c r="J328" s="26"/>
+      <c r="K328" s="26"/>
+      <c r="L328" s="26"/>
+      <c r="M328" s="26"/>
     </row>
     <row r="329">
-      <c r="A329" s="24"/>
-      <c r="B329" s="24"/>
-      <c r="C329" s="24"/>
-      <c r="D329" s="24"/>
-      <c r="E329" s="24"/>
-      <c r="F329" s="24"/>
-      <c r="G329" s="24"/>
-      <c r="H329" s="25"/>
-      <c r="I329" s="25"/>
-      <c r="J329" s="25"/>
-      <c r="K329" s="25"/>
-      <c r="L329" s="25"/>
-      <c r="M329" s="25"/>
+      <c r="A329" s="25"/>
+      <c r="B329" s="25"/>
+      <c r="C329" s="25"/>
+      <c r="D329" s="25"/>
+      <c r="E329" s="25"/>
+      <c r="F329" s="25"/>
+      <c r="G329" s="25"/>
+      <c r="H329" s="26"/>
+      <c r="I329" s="26"/>
+      <c r="J329" s="26"/>
+      <c r="K329" s="26"/>
+      <c r="L329" s="26"/>
+      <c r="M329" s="26"/>
     </row>
     <row r="330">
-      <c r="A330" s="24"/>
-      <c r="B330" s="24"/>
-      <c r="C330" s="24"/>
-      <c r="D330" s="24"/>
-      <c r="E330" s="24"/>
-      <c r="F330" s="24"/>
-      <c r="G330" s="24"/>
-      <c r="H330" s="25"/>
-      <c r="I330" s="25"/>
-      <c r="J330" s="25"/>
-      <c r="K330" s="25"/>
-      <c r="L330" s="25"/>
-      <c r="M330" s="25"/>
+      <c r="A330" s="25"/>
+      <c r="B330" s="25"/>
+      <c r="C330" s="25"/>
+      <c r="D330" s="25"/>
+      <c r="E330" s="25"/>
+      <c r="F330" s="25"/>
+      <c r="G330" s="25"/>
+      <c r="H330" s="26"/>
+      <c r="I330" s="26"/>
+      <c r="J330" s="26"/>
+      <c r="K330" s="26"/>
+      <c r="L330" s="26"/>
+      <c r="M330" s="26"/>
     </row>
     <row r="331">
-      <c r="A331" s="24"/>
-      <c r="B331" s="24"/>
-      <c r="C331" s="24"/>
-      <c r="D331" s="24"/>
-      <c r="E331" s="24"/>
-      <c r="F331" s="24"/>
-      <c r="G331" s="24"/>
-      <c r="H331" s="25"/>
-      <c r="I331" s="25"/>
-      <c r="J331" s="25"/>
-      <c r="K331" s="25"/>
-      <c r="L331" s="25"/>
-      <c r="M331" s="25"/>
+      <c r="A331" s="25"/>
+      <c r="B331" s="25"/>
+      <c r="C331" s="25"/>
+      <c r="D331" s="25"/>
+      <c r="E331" s="25"/>
+      <c r="F331" s="25"/>
+      <c r="G331" s="25"/>
+      <c r="H331" s="26"/>
+      <c r="I331" s="26"/>
+      <c r="J331" s="26"/>
+      <c r="K331" s="26"/>
+      <c r="L331" s="26"/>
+      <c r="M331" s="26"/>
     </row>
     <row r="332">
-      <c r="A332" s="24"/>
-      <c r="B332" s="24"/>
-      <c r="C332" s="24"/>
-      <c r="D332" s="24"/>
-      <c r="E332" s="24"/>
-      <c r="F332" s="24"/>
-      <c r="G332" s="24"/>
-      <c r="H332" s="25"/>
-      <c r="I332" s="25"/>
-      <c r="J332" s="25"/>
-      <c r="K332" s="25"/>
-      <c r="L332" s="25"/>
-      <c r="M332" s="25"/>
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+      <c r="D332" s="25"/>
+      <c r="E332" s="25"/>
+      <c r="F332" s="25"/>
+      <c r="G332" s="25"/>
+      <c r="H332" s="26"/>
+      <c r="I332" s="26"/>
+      <c r="J332" s="26"/>
+      <c r="K332" s="26"/>
+      <c r="L332" s="26"/>
+      <c r="M332" s="26"/>
     </row>
     <row r="333">
-      <c r="A333" s="24"/>
-      <c r="B333" s="24"/>
-      <c r="C333" s="24"/>
-      <c r="D333" s="24"/>
-      <c r="E333" s="24"/>
-      <c r="F333" s="24"/>
-      <c r="G333" s="24"/>
-      <c r="H333" s="25"/>
-      <c r="I333" s="25"/>
-      <c r="J333" s="25"/>
-      <c r="K333" s="25"/>
-      <c r="L333" s="25"/>
-      <c r="M333" s="25"/>
+      <c r="A333" s="25"/>
+      <c r="B333" s="25"/>
+      <c r="C333" s="25"/>
+      <c r="D333" s="25"/>
+      <c r="E333" s="25"/>
+      <c r="F333" s="25"/>
+      <c r="G333" s="25"/>
+      <c r="H333" s="26"/>
+      <c r="I333" s="26"/>
+      <c r="J333" s="26"/>
+      <c r="K333" s="26"/>
+      <c r="L333" s="26"/>
+      <c r="M333" s="26"/>
     </row>
     <row r="334">
-      <c r="A334" s="24"/>
-      <c r="B334" s="24"/>
-      <c r="C334" s="24"/>
-      <c r="D334" s="24"/>
-      <c r="E334" s="24"/>
-      <c r="F334" s="24"/>
-      <c r="G334" s="24"/>
-      <c r="H334" s="25"/>
-      <c r="I334" s="25"/>
-      <c r="J334" s="25"/>
-      <c r="K334" s="25"/>
-      <c r="L334" s="25"/>
-      <c r="M334" s="25"/>
+      <c r="A334" s="25"/>
+      <c r="B334" s="25"/>
+      <c r="C334" s="25"/>
+      <c r="D334" s="25"/>
+      <c r="E334" s="25"/>
+      <c r="F334" s="25"/>
+      <c r="G334" s="25"/>
+      <c r="H334" s="26"/>
+      <c r="I334" s="26"/>
+      <c r="J334" s="26"/>
+      <c r="K334" s="26"/>
+      <c r="L334" s="26"/>
+      <c r="M334" s="26"/>
     </row>
     <row r="335">
-      <c r="A335" s="24"/>
-      <c r="B335" s="24"/>
-      <c r="C335" s="24"/>
-      <c r="D335" s="24"/>
-      <c r="E335" s="24"/>
-      <c r="F335" s="24"/>
-      <c r="G335" s="24"/>
-      <c r="H335" s="25"/>
-      <c r="I335" s="25"/>
-      <c r="J335" s="25"/>
-      <c r="K335" s="25"/>
-      <c r="L335" s="25"/>
-      <c r="M335" s="25"/>
+      <c r="A335" s="25"/>
+      <c r="B335" s="25"/>
+      <c r="C335" s="25"/>
+      <c r="D335" s="25"/>
+      <c r="E335" s="25"/>
+      <c r="F335" s="25"/>
+      <c r="G335" s="25"/>
+      <c r="H335" s="26"/>
+      <c r="I335" s="26"/>
+      <c r="J335" s="26"/>
+      <c r="K335" s="26"/>
+      <c r="L335" s="26"/>
+      <c r="M335" s="26"/>
     </row>
     <row r="336">
-      <c r="A336" s="24"/>
-      <c r="B336" s="24"/>
-      <c r="C336" s="24"/>
-      <c r="D336" s="24"/>
-      <c r="E336" s="24"/>
-      <c r="F336" s="24"/>
-      <c r="G336" s="24"/>
-      <c r="H336" s="25"/>
-      <c r="I336" s="25"/>
-      <c r="J336" s="25"/>
-      <c r="K336" s="25"/>
-      <c r="L336" s="25"/>
-      <c r="M336" s="25"/>
+      <c r="A336" s="25"/>
+      <c r="B336" s="25"/>
+      <c r="C336" s="25"/>
+      <c r="D336" s="25"/>
+      <c r="E336" s="25"/>
+      <c r="F336" s="25"/>
+      <c r="G336" s="25"/>
+      <c r="H336" s="26"/>
+      <c r="I336" s="26"/>
+      <c r="J336" s="26"/>
+      <c r="K336" s="26"/>
+      <c r="L336" s="26"/>
+      <c r="M336" s="26"/>
     </row>
     <row r="337">
-      <c r="A337" s="24"/>
-      <c r="B337" s="24"/>
-      <c r="C337" s="24"/>
-      <c r="D337" s="24"/>
-      <c r="E337" s="24"/>
-      <c r="F337" s="24"/>
-      <c r="G337" s="24"/>
-      <c r="H337" s="25"/>
-      <c r="I337" s="25"/>
-      <c r="J337" s="25"/>
-      <c r="K337" s="25"/>
-      <c r="L337" s="25"/>
-      <c r="M337" s="25"/>
+      <c r="A337" s="25"/>
+      <c r="B337" s="25"/>
+      <c r="C337" s="25"/>
+      <c r="D337" s="25"/>
+      <c r="E337" s="25"/>
+      <c r="F337" s="25"/>
+      <c r="G337" s="25"/>
+      <c r="H337" s="26"/>
+      <c r="I337" s="26"/>
+      <c r="J337" s="26"/>
+      <c r="K337" s="26"/>
+      <c r="L337" s="26"/>
+      <c r="M337" s="26"/>
     </row>
     <row r="338">
-      <c r="A338" s="24"/>
-      <c r="B338" s="24"/>
-      <c r="C338" s="24"/>
-      <c r="D338" s="24"/>
-      <c r="E338" s="24"/>
-      <c r="F338" s="24"/>
-      <c r="G338" s="24"/>
-      <c r="H338" s="25"/>
-      <c r="I338" s="25"/>
-      <c r="J338" s="25"/>
-      <c r="K338" s="25"/>
-      <c r="L338" s="25"/>
-      <c r="M338" s="25"/>
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+      <c r="D338" s="25"/>
+      <c r="E338" s="25"/>
+      <c r="F338" s="25"/>
+      <c r="G338" s="25"/>
+      <c r="H338" s="26"/>
+      <c r="I338" s="26"/>
+      <c r="J338" s="26"/>
+      <c r="K338" s="26"/>
+      <c r="L338" s="26"/>
+      <c r="M338" s="26"/>
     </row>
     <row r="339">
-      <c r="A339" s="24"/>
-      <c r="B339" s="24"/>
-      <c r="C339" s="24"/>
-      <c r="D339" s="24"/>
-      <c r="E339" s="24"/>
-      <c r="F339" s="24"/>
-      <c r="G339" s="24"/>
-      <c r="H339" s="25"/>
-      <c r="I339" s="25"/>
-      <c r="J339" s="25"/>
-      <c r="K339" s="25"/>
-      <c r="L339" s="25"/>
-      <c r="M339" s="25"/>
+      <c r="A339" s="25"/>
+      <c r="B339" s="25"/>
+      <c r="C339" s="25"/>
+      <c r="D339" s="25"/>
+      <c r="E339" s="25"/>
+      <c r="F339" s="25"/>
+      <c r="G339" s="25"/>
+      <c r="H339" s="26"/>
+      <c r="I339" s="26"/>
+      <c r="J339" s="26"/>
+      <c r="K339" s="26"/>
+      <c r="L339" s="26"/>
+      <c r="M339" s="26"/>
     </row>
     <row r="340">
-      <c r="A340" s="24"/>
-      <c r="B340" s="24"/>
-      <c r="C340" s="24"/>
-      <c r="D340" s="24"/>
-      <c r="E340" s="24"/>
-      <c r="F340" s="24"/>
-      <c r="G340" s="24"/>
-      <c r="H340" s="25"/>
-      <c r="I340" s="25"/>
-      <c r="J340" s="25"/>
-      <c r="K340" s="25"/>
-      <c r="L340" s="25"/>
-      <c r="M340" s="25"/>
+      <c r="A340" s="25"/>
+      <c r="B340" s="25"/>
+      <c r="C340" s="25"/>
+      <c r="D340" s="25"/>
+      <c r="E340" s="25"/>
+      <c r="F340" s="25"/>
+      <c r="G340" s="25"/>
+      <c r="H340" s="26"/>
+      <c r="I340" s="26"/>
+      <c r="J340" s="26"/>
+      <c r="K340" s="26"/>
+      <c r="L340" s="26"/>
+      <c r="M340" s="26"/>
     </row>
     <row r="341">
-      <c r="A341" s="24"/>
-      <c r="B341" s="24"/>
-      <c r="C341" s="24"/>
-      <c r="D341" s="24"/>
-      <c r="E341" s="24"/>
-      <c r="F341" s="24"/>
-      <c r="G341" s="24"/>
-      <c r="H341" s="25"/>
-      <c r="I341" s="25"/>
-      <c r="J341" s="25"/>
-      <c r="K341" s="25"/>
-      <c r="L341" s="25"/>
-      <c r="M341" s="25"/>
+      <c r="A341" s="25"/>
+      <c r="B341" s="25"/>
+      <c r="C341" s="25"/>
+      <c r="D341" s="25"/>
+      <c r="E341" s="25"/>
+      <c r="F341" s="25"/>
+      <c r="G341" s="25"/>
+      <c r="H341" s="26"/>
+      <c r="I341" s="26"/>
+      <c r="J341" s="26"/>
+      <c r="K341" s="26"/>
+      <c r="L341" s="26"/>
+      <c r="M341" s="26"/>
     </row>
     <row r="342">
-      <c r="A342" s="24"/>
-      <c r="B342" s="24"/>
-      <c r="C342" s="24"/>
-      <c r="D342" s="24"/>
-      <c r="E342" s="24"/>
-      <c r="F342" s="24"/>
-      <c r="G342" s="24"/>
-      <c r="H342" s="25"/>
-      <c r="I342" s="25"/>
-      <c r="J342" s="25"/>
-      <c r="K342" s="25"/>
-      <c r="L342" s="25"/>
-      <c r="M342" s="25"/>
+      <c r="A342" s="25"/>
+      <c r="B342" s="25"/>
+      <c r="C342" s="25"/>
+      <c r="D342" s="25"/>
+      <c r="E342" s="25"/>
+      <c r="F342" s="25"/>
+      <c r="G342" s="25"/>
+      <c r="H342" s="26"/>
+      <c r="I342" s="26"/>
+      <c r="J342" s="26"/>
+      <c r="K342" s="26"/>
+      <c r="L342" s="26"/>
+      <c r="M342" s="26"/>
     </row>
     <row r="343">
-      <c r="A343" s="24"/>
-      <c r="B343" s="24"/>
-      <c r="C343" s="24"/>
-      <c r="D343" s="24"/>
-      <c r="E343" s="24"/>
-      <c r="F343" s="24"/>
-      <c r="G343" s="24"/>
-      <c r="H343" s="25"/>
-      <c r="I343" s="25"/>
-      <c r="J343" s="25"/>
-      <c r="K343" s="25"/>
-      <c r="L343" s="25"/>
-      <c r="M343" s="25"/>
+      <c r="A343" s="25"/>
+      <c r="B343" s="25"/>
+      <c r="C343" s="25"/>
+      <c r="D343" s="25"/>
+      <c r="E343" s="25"/>
+      <c r="F343" s="25"/>
+      <c r="G343" s="25"/>
+      <c r="H343" s="26"/>
+      <c r="I343" s="26"/>
+      <c r="J343" s="26"/>
+      <c r="K343" s="26"/>
+      <c r="L343" s="26"/>
+      <c r="M343" s="26"/>
     </row>
     <row r="344">
-      <c r="A344" s="24"/>
-      <c r="B344" s="24"/>
-      <c r="C344" s="24"/>
-      <c r="D344" s="24"/>
-      <c r="E344" s="24"/>
-      <c r="F344" s="24"/>
-      <c r="G344" s="24"/>
-      <c r="H344" s="25"/>
-      <c r="I344" s="25"/>
-      <c r="J344" s="25"/>
-      <c r="K344" s="25"/>
-      <c r="L344" s="25"/>
-      <c r="M344" s="25"/>
+      <c r="A344" s="25"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+      <c r="D344" s="25"/>
+      <c r="E344" s="25"/>
+      <c r="F344" s="25"/>
+      <c r="G344" s="25"/>
+      <c r="H344" s="26"/>
+      <c r="I344" s="26"/>
+      <c r="J344" s="26"/>
+      <c r="K344" s="26"/>
+      <c r="L344" s="26"/>
+      <c r="M344" s="26"/>
     </row>
     <row r="345">
-      <c r="A345" s="24"/>
-      <c r="B345" s="24"/>
-      <c r="C345" s="24"/>
-      <c r="D345" s="24"/>
-      <c r="E345" s="24"/>
-      <c r="F345" s="24"/>
-      <c r="G345" s="24"/>
-      <c r="H345" s="25"/>
-      <c r="I345" s="25"/>
-      <c r="J345" s="25"/>
-      <c r="K345" s="25"/>
-      <c r="L345" s="25"/>
-      <c r="M345" s="25"/>
+      <c r="A345" s="25"/>
+      <c r="B345" s="25"/>
+      <c r="C345" s="25"/>
+      <c r="D345" s="25"/>
+      <c r="E345" s="25"/>
+      <c r="F345" s="25"/>
+      <c r="G345" s="25"/>
+      <c r="H345" s="26"/>
+      <c r="I345" s="26"/>
+      <c r="J345" s="26"/>
+      <c r="K345" s="26"/>
+      <c r="L345" s="26"/>
+      <c r="M345" s="26"/>
     </row>
     <row r="346">
-      <c r="A346" s="24"/>
-      <c r="B346" s="24"/>
-      <c r="C346" s="24"/>
-      <c r="D346" s="24"/>
-      <c r="E346" s="24"/>
-      <c r="F346" s="24"/>
-      <c r="G346" s="24"/>
-      <c r="H346" s="25"/>
-      <c r="I346" s="25"/>
-      <c r="J346" s="25"/>
-      <c r="K346" s="25"/>
-      <c r="L346" s="25"/>
-      <c r="M346" s="25"/>
+      <c r="A346" s="25"/>
+      <c r="B346" s="25"/>
+      <c r="C346" s="25"/>
+      <c r="D346" s="25"/>
+      <c r="E346" s="25"/>
+      <c r="F346" s="25"/>
+      <c r="G346" s="25"/>
+      <c r="H346" s="26"/>
+      <c r="I346" s="26"/>
+      <c r="J346" s="26"/>
+      <c r="K346" s="26"/>
+      <c r="L346" s="26"/>
+      <c r="M346" s="26"/>
     </row>
     <row r="347">
-      <c r="A347" s="24"/>
-      <c r="B347" s="24"/>
-      <c r="C347" s="24"/>
-      <c r="D347" s="24"/>
-      <c r="E347" s="24"/>
-      <c r="F347" s="24"/>
-      <c r="G347" s="24"/>
-      <c r="H347" s="25"/>
-      <c r="I347" s="25"/>
-      <c r="J347" s="25"/>
-      <c r="K347" s="25"/>
-      <c r="L347" s="25"/>
-      <c r="M347" s="25"/>
+      <c r="A347" s="25"/>
+      <c r="B347" s="25"/>
+      <c r="C347" s="25"/>
+      <c r="D347" s="25"/>
+      <c r="E347" s="25"/>
+      <c r="F347" s="25"/>
+      <c r="G347" s="25"/>
+      <c r="H347" s="26"/>
+      <c r="I347" s="26"/>
+      <c r="J347" s="26"/>
+      <c r="K347" s="26"/>
+      <c r="L347" s="26"/>
+      <c r="M347" s="26"/>
     </row>
     <row r="348">
-      <c r="A348" s="24"/>
-      <c r="B348" s="24"/>
-      <c r="C348" s="24"/>
-      <c r="D348" s="24"/>
-      <c r="E348" s="24"/>
-      <c r="F348" s="24"/>
-      <c r="G348" s="24"/>
-      <c r="H348" s="25"/>
-      <c r="I348" s="25"/>
-      <c r="J348" s="25"/>
-      <c r="K348" s="25"/>
-      <c r="L348" s="25"/>
-      <c r="M348" s="25"/>
+      <c r="A348" s="25"/>
+      <c r="B348" s="25"/>
+      <c r="C348" s="25"/>
+      <c r="D348" s="25"/>
+      <c r="E348" s="25"/>
+      <c r="F348" s="25"/>
+      <c r="G348" s="25"/>
+      <c r="H348" s="26"/>
+      <c r="I348" s="26"/>
+      <c r="J348" s="26"/>
+      <c r="K348" s="26"/>
+      <c r="L348" s="26"/>
+      <c r="M348" s="26"/>
     </row>
     <row r="349">
-      <c r="A349" s="24"/>
-      <c r="B349" s="24"/>
-      <c r="C349" s="24"/>
-      <c r="D349" s="24"/>
-      <c r="E349" s="24"/>
-      <c r="F349" s="24"/>
-      <c r="G349" s="24"/>
-      <c r="H349" s="25"/>
-      <c r="I349" s="25"/>
-      <c r="J349" s="25"/>
-      <c r="K349" s="25"/>
-      <c r="L349" s="25"/>
-      <c r="M349" s="25"/>
+      <c r="A349" s="25"/>
+      <c r="B349" s="25"/>
+      <c r="C349" s="25"/>
+      <c r="D349" s="25"/>
+      <c r="E349" s="25"/>
+      <c r="F349" s="25"/>
+      <c r="G349" s="25"/>
+      <c r="H349" s="26"/>
+      <c r="I349" s="26"/>
+      <c r="J349" s="26"/>
+      <c r="K349" s="26"/>
+      <c r="L349" s="26"/>
+      <c r="M349" s="26"/>
     </row>
     <row r="350">
-      <c r="A350" s="24"/>
-      <c r="B350" s="24"/>
-      <c r="C350" s="24"/>
-      <c r="D350" s="24"/>
-      <c r="E350" s="24"/>
-      <c r="F350" s="24"/>
-      <c r="G350" s="24"/>
-      <c r="H350" s="25"/>
-      <c r="I350" s="25"/>
-      <c r="J350" s="25"/>
-      <c r="K350" s="25"/>
-      <c r="L350" s="25"/>
-      <c r="M350" s="25"/>
+      <c r="A350" s="25"/>
+      <c r="B350" s="25"/>
+      <c r="C350" s="25"/>
+      <c r="D350" s="25"/>
+      <c r="E350" s="25"/>
+      <c r="F350" s="25"/>
+      <c r="G350" s="25"/>
+      <c r="H350" s="26"/>
+      <c r="I350" s="26"/>
+      <c r="J350" s="26"/>
+      <c r="K350" s="26"/>
+      <c r="L350" s="26"/>
+      <c r="M350" s="26"/>
     </row>
     <row r="351">
-      <c r="A351" s="24"/>
-      <c r="B351" s="24"/>
-      <c r="C351" s="24"/>
-      <c r="D351" s="24"/>
-      <c r="E351" s="24"/>
-      <c r="F351" s="24"/>
-      <c r="G351" s="24"/>
-      <c r="H351" s="25"/>
-      <c r="I351" s="25"/>
-      <c r="J351" s="25"/>
-      <c r="K351" s="25"/>
-      <c r="L351" s="25"/>
-      <c r="M351" s="25"/>
+      <c r="A351" s="25"/>
+      <c r="B351" s="25"/>
+      <c r="C351" s="25"/>
+      <c r="D351" s="25"/>
+      <c r="E351" s="25"/>
+      <c r="F351" s="25"/>
+      <c r="G351" s="25"/>
+      <c r="H351" s="26"/>
+      <c r="I351" s="26"/>
+      <c r="J351" s="26"/>
+      <c r="K351" s="26"/>
+      <c r="L351" s="26"/>
+      <c r="M351" s="26"/>
     </row>
     <row r="352">
-      <c r="A352" s="24"/>
-      <c r="B352" s="24"/>
-      <c r="C352" s="24"/>
-      <c r="D352" s="24"/>
-      <c r="E352" s="24"/>
-      <c r="F352" s="24"/>
-      <c r="G352" s="24"/>
-      <c r="H352" s="25"/>
-      <c r="I352" s="25"/>
-      <c r="J352" s="25"/>
-      <c r="K352" s="25"/>
-      <c r="L352" s="25"/>
-      <c r="M352" s="25"/>
+      <c r="A352" s="25"/>
+      <c r="B352" s="25"/>
+      <c r="C352" s="25"/>
+      <c r="D352" s="25"/>
+      <c r="E352" s="25"/>
+      <c r="F352" s="25"/>
+      <c r="G352" s="25"/>
+      <c r="H352" s="26"/>
+      <c r="I352" s="26"/>
+      <c r="J352" s="26"/>
+      <c r="K352" s="26"/>
+      <c r="L352" s="26"/>
+      <c r="M352" s="26"/>
     </row>
     <row r="353">
-      <c r="A353" s="24"/>
-      <c r="B353" s="24"/>
-      <c r="C353" s="24"/>
-      <c r="D353" s="24"/>
-      <c r="E353" s="24"/>
-      <c r="F353" s="24"/>
-      <c r="G353" s="24"/>
-      <c r="H353" s="25"/>
-      <c r="I353" s="25"/>
-      <c r="J353" s="25"/>
-      <c r="K353" s="25"/>
-      <c r="L353" s="25"/>
-      <c r="M353" s="25"/>
+      <c r="A353" s="25"/>
+      <c r="B353" s="25"/>
+      <c r="C353" s="25"/>
+      <c r="D353" s="25"/>
+      <c r="E353" s="25"/>
+      <c r="F353" s="25"/>
+      <c r="G353" s="25"/>
+      <c r="H353" s="26"/>
+      <c r="I353" s="26"/>
+      <c r="J353" s="26"/>
+      <c r="K353" s="26"/>
+      <c r="L353" s="26"/>
+      <c r="M353" s="26"/>
     </row>
     <row r="354">
-      <c r="A354" s="24"/>
-      <c r="B354" s="24"/>
-      <c r="C354" s="24"/>
-      <c r="D354" s="24"/>
-      <c r="E354" s="24"/>
-      <c r="F354" s="24"/>
-      <c r="G354" s="24"/>
-      <c r="H354" s="25"/>
-      <c r="I354" s="25"/>
-      <c r="J354" s="25"/>
-      <c r="K354" s="25"/>
-      <c r="L354" s="25"/>
-      <c r="M354" s="25"/>
+      <c r="A354" s="25"/>
+      <c r="B354" s="25"/>
+      <c r="C354" s="25"/>
+      <c r="D354" s="25"/>
+      <c r="E354" s="25"/>
+      <c r="F354" s="25"/>
+      <c r="G354" s="25"/>
+      <c r="H354" s="26"/>
+      <c r="I354" s="26"/>
+      <c r="J354" s="26"/>
+      <c r="K354" s="26"/>
+      <c r="L354" s="26"/>
+      <c r="M354" s="26"/>
     </row>
     <row r="355">
-      <c r="A355" s="24"/>
-      <c r="B355" s="24"/>
-      <c r="C355" s="24"/>
-      <c r="D355" s="24"/>
-      <c r="E355" s="24"/>
-      <c r="F355" s="24"/>
-      <c r="G355" s="24"/>
-      <c r="H355" s="25"/>
-      <c r="I355" s="25"/>
-      <c r="J355" s="25"/>
-      <c r="K355" s="25"/>
-      <c r="L355" s="25"/>
-      <c r="M355" s="25"/>
+      <c r="A355" s="25"/>
+      <c r="B355" s="25"/>
+      <c r="C355" s="25"/>
+      <c r="D355" s="25"/>
+      <c r="E355" s="25"/>
+      <c r="F355" s="25"/>
+      <c r="G355" s="25"/>
+      <c r="H355" s="26"/>
+      <c r="I355" s="26"/>
+      <c r="J355" s="26"/>
+      <c r="K355" s="26"/>
+      <c r="L355" s="26"/>
+      <c r="M355" s="26"/>
     </row>
     <row r="356">
-      <c r="A356" s="24"/>
-      <c r="B356" s="24"/>
-      <c r="C356" s="24"/>
-      <c r="D356" s="24"/>
-      <c r="E356" s="24"/>
-      <c r="F356" s="24"/>
-      <c r="G356" s="24"/>
-      <c r="H356" s="25"/>
-      <c r="I356" s="25"/>
-      <c r="J356" s="25"/>
-      <c r="K356" s="25"/>
-      <c r="L356" s="25"/>
-      <c r="M356" s="25"/>
+      <c r="A356" s="25"/>
+      <c r="B356" s="25"/>
+      <c r="C356" s="25"/>
+      <c r="D356" s="25"/>
+      <c r="E356" s="25"/>
+      <c r="F356" s="25"/>
+      <c r="G356" s="25"/>
+      <c r="H356" s="26"/>
+      <c r="I356" s="26"/>
+      <c r="J356" s="26"/>
+      <c r="K356" s="26"/>
+      <c r="L356" s="26"/>
+      <c r="M356" s="26"/>
     </row>
     <row r="357">
-      <c r="A357" s="24"/>
-      <c r="B357" s="24"/>
-      <c r="C357" s="24"/>
-      <c r="D357" s="24"/>
-      <c r="E357" s="24"/>
-      <c r="F357" s="24"/>
-      <c r="G357" s="24"/>
-      <c r="H357" s="25"/>
-      <c r="I357" s="25"/>
-      <c r="J357" s="25"/>
-      <c r="K357" s="25"/>
-      <c r="L357" s="25"/>
-      <c r="M357" s="25"/>
+      <c r="A357" s="25"/>
+      <c r="B357" s="25"/>
+      <c r="C357" s="25"/>
+      <c r="D357" s="25"/>
+      <c r="E357" s="25"/>
+      <c r="F357" s="25"/>
+      <c r="G357" s="25"/>
+      <c r="H357" s="26"/>
+      <c r="I357" s="26"/>
+      <c r="J357" s="26"/>
+      <c r="K357" s="26"/>
+      <c r="L357" s="26"/>
+      <c r="M357" s="26"/>
     </row>
     <row r="358">
-      <c r="A358" s="24"/>
-      <c r="B358" s="24"/>
-      <c r="C358" s="24"/>
-      <c r="D358" s="24"/>
-      <c r="E358" s="24"/>
-      <c r="F358" s="24"/>
-      <c r="G358" s="24"/>
-      <c r="H358" s="25"/>
-      <c r="I358" s="25"/>
-      <c r="J358" s="25"/>
-      <c r="K358" s="25"/>
-      <c r="L358" s="25"/>
-      <c r="M358" s="25"/>
+      <c r="A358" s="25"/>
+      <c r="B358" s="25"/>
+      <c r="C358" s="25"/>
+      <c r="D358" s="25"/>
+      <c r="E358" s="25"/>
+      <c r="F358" s="25"/>
+      <c r="G358" s="25"/>
+      <c r="H358" s="26"/>
+      <c r="I358" s="26"/>
+      <c r="J358" s="26"/>
+      <c r="K358" s="26"/>
+      <c r="L358" s="26"/>
+      <c r="M358" s="26"/>
     </row>
     <row r="359">
-      <c r="A359" s="24"/>
-      <c r="B359" s="24"/>
-      <c r="C359" s="24"/>
-      <c r="D359" s="24"/>
-      <c r="E359" s="24"/>
-      <c r="F359" s="24"/>
-      <c r="G359" s="24"/>
-      <c r="H359" s="25"/>
-      <c r="I359" s="25"/>
-      <c r="J359" s="25"/>
-      <c r="K359" s="25"/>
-      <c r="L359" s="25"/>
-      <c r="M359" s="25"/>
+      <c r="A359" s="25"/>
+      <c r="B359" s="25"/>
+      <c r="C359" s="25"/>
+      <c r="D359" s="25"/>
+      <c r="E359" s="25"/>
+      <c r="F359" s="25"/>
+      <c r="G359" s="25"/>
+      <c r="H359" s="26"/>
+      <c r="I359" s="26"/>
+      <c r="J359" s="26"/>
+      <c r="K359" s="26"/>
+      <c r="L359" s="26"/>
+      <c r="M359" s="26"/>
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{BA280C03-A6D0-4DDC-8248-3342070E140F}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{6CFFF1F8-EEAD-47B1-A5BA-9B98655A952B}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{6C1217AC-2F5B-4B9C-9906-85A2A50A1B7D}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{42D6E9FA-5371-4DCF-B97C-438E291F0C15}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{7356B801-1C63-4121-8D46-7701FF85BCCF}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{1B3A8ACD-D417-4637-A685-81D9381FF1DE}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{85EBEFAE-B28A-4127-B6B4-6AC4CCC8C134}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{E19D6905-7219-4716-8E35-399AC7C1BC00}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{CCFC2D6D-1682-4A8C-B48A-667DB9857DDD}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{ECF78DD8-3C13-45CB-A702-9BDF29315AF0}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{6A080B14-C65B-46DD-97E6-498C19CD9206}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{6EA19BB9-567C-4055-96CB-2C19019C8916}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{855D6783-E89F-4AEB-97D0-945807C7153F}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{8AACF8F8-B55E-4915-9F46-991C008EBE09}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{306D586A-A5AC-4229-9E1C-5457B85CC7A8}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{1EA62444-B123-4C0B-8F7F-3B200448A206}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{3A2C5092-5A3C-4B76-8D10-65234E69162B}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{B42CC50D-F60F-42F9-B8C0-FC77153034DE}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29">
         <sortState ref="A1:M29">
           <sortCondition ref="F1:F29"/>
         </sortState>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{0367D160-10D3-45F3-A48E-CCB1E25EADB5}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{D6D6AAF0-767B-47ED-B3D3-B6430EEAFC24}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29">
         <sortState ref="A1:M29">
           <sortCondition ref="G1:G29"/>
         </sortState>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{AAFBD7D5-478E-4F1A-B903-212B193B56E9}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{BDCCA16F-5B03-4638-AFE1-84255B44CB7F}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
   </customSheetViews>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="portrait" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
   <tableParts count="2">
     <tablePart r:id="rId4"/>

--- a/result.xlsx
+++ b/result.xlsx
@@ -6,31 +6,31 @@
     <sheet state="visible" name="5th" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_ECF78DD8_3C13_45CB_A702_9BDF29315AF0_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_8AACF8F8_B55E_4915_9F46_991C008EBE09_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_B42CC50D_F60F_42F9_B8C0_FC77153034DE_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_6EA19BB9_567C_4055_96CB_2C19019C8916_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_1EA62444_B123_4C0B_8F7F_3B200448A206_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_BDCCA16F_5B03_4638_AFE1_84255B44CB7F_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_6CFFF1F8_EEAD_47B1_A5BA_9B98655A952B_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_42D6E9FA_5371_4DCF_B97C_438E291F0C15_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_D6D6AAF0_767B_47ED_B3D3_B6430EEAFC24_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_E19D6905_7219_4716_8E35_399AC7C1BC00_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_1B3A8ACD_D417_4637_A685_81D9381FF1DE_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_98289A86_091A_432E_95EB_62C0CCB6E499_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_7E949F86_CBBE_4D4A_B11E_3032717324AC_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_018C47CD_611C_4A4D_9F70_D959A33B0A04_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_7DCAD69D_5D4D_42D8_AF66_6922AFF61F41_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_9EF01319_1434_4553_ABA9_8A8DB3118517_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_D4852FD5_0F09_401B_B4EA_0D373D545BD2_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_04333B8C_AC3F_4D65_9552_CFEC1FEC2F88_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_55AED9A0_DA0D_4128_B5D2_1BF8D79ECD96_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_00AEBA2B_1B46_4428_9543_9DBC253D4359_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_1DF0D9CB_1060_4CA2_8949_B31DCBD5B4BF_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_113A483A_B910_44BD_9A0A_C77FF7CF5327_.wvu.FilterData">'5th'!$A$1:$M$29</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{8AACF8F8-B55E-4915-9F46-991C008EBE09}" name="Group by School Name [2]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{6EA19BB9-567C-4055-96CB-2C19019C8916}" name="Group by School Name [3]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ECF78DD8-3C13-45CB-A702-9BDF29315AF0}" name="Group by School Name [6]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{B42CC50D-F60F-42F9-B8C0-FC77153034DE}" name="Group by School Name [7]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{E19D6905-7219-4716-8E35-399AC7C1BC00}" name="Group by School Name [4]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{42D6E9FA-5371-4DCF-B97C-438E291F0C15}" name="Group by School Name [5]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{1EA62444-B123-4C0B-8F7F-3B200448A206}" name="Group by School Name [8]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{BDCCA16F-5B03-4638-AFE1-84255B44CB7F}" name="Group by Class"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{1B3A8ACD-D417-4637-A685-81D9381FF1DE}" name="Group by Class [3]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{D6D6AAF0-767B-47ED-B3D3-B6430EEAFC24}" name="Group by Class [2]"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{6CFFF1F8-EEAD-47B1-A5BA-9B98655A952B}" name="Group by School Name"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{04333B8C-AC3F-4D65-9552-CFEC1FEC2F88}" name="Group by School Name [2]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{D4852FD5-0F09-401B-B4EA-0D373D545BD2}" name="Group by School Name [3]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{113A483A-B910-44BD-9A0A-C77FF7CF5327}" name="Group by School Name [6]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{00AEBA2B-1B46-4428-9543-9DBC253D4359}" name="Group by School Name [7]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{018C47CD-611C-4A4D-9F70-D959A33B0A04}" name="Group by School Name [4]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{1DF0D9CB-1060-4CA2-8949-B31DCBD5B4BF}" name="Group by School Name [5]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{7E949F86-CBBE-4D4A-B11E-3032717324AC}" name="Group by School Name [8]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{7DCAD69D-5D4D-42D8-AF66-6922AFF61F41}" name="Group by Class"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{55AED9A0-DA0D-4128-B5D2-1BF8D79ECD96}" name="Group by Class [3]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{9EF01319-1434-4553-ABA9-8A8DB3118517}" name="Group by Class [2]"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{98289A86-091A-432E-95EB-62C0CCB6E499}" name="Group by School Name"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -1187,10 +1187,10 @@
     <t>FAP26-EAE-07-05</t>
   </si>
   <si>
-    <t>SHURAV KUMAR</t>
-  </si>
-  <si>
-    <t>ANAIL SINGH</t>
+    <t>SAURAV KUMAR</t>
+  </si>
+  <si>
+    <t>ANIL SINGH</t>
   </si>
   <si>
     <t>FAP26-EAE-113</t>
@@ -1235,7 +1235,7 @@
     <t>FAP26-EAE-07-09</t>
   </si>
   <si>
-    <t>SOHAIB ANSARI</t>
+    <t>SOAIB ANSARI</t>
   </si>
   <si>
     <t>NIZAM ANSARI</t>
@@ -3784,7 +3784,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3838,6 +3838,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
@@ -8078,10 +8081,10 @@
       <c r="B94" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="D94" s="19" t="s">
         <v>384</v>
       </c>
       <c r="E94" s="14" t="s">
@@ -8246,7 +8249,7 @@
       <c r="B98" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="19" t="s">
         <v>399</v>
       </c>
       <c r="D98" s="14" t="s">
@@ -10862,33 +10865,33 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="19" t="s">
+      <c r="A161" s="20" t="s">
         <v>630</v>
       </c>
-      <c r="B161" s="20" t="s">
+      <c r="B161" s="21" t="s">
         <v>631</v>
       </c>
-      <c r="C161" s="19" t="s">
+      <c r="C161" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D161" s="19" t="s">
+      <c r="D161" s="20" t="s">
         <v>633</v>
       </c>
-      <c r="E161" s="20" t="s">
+      <c r="E161" s="21" t="s">
         <v>634</v>
       </c>
-      <c r="F161" s="19" t="s">
+      <c r="F161" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G161" s="19" t="s">
+      <c r="G161" s="20" t="s">
         <v>635</v>
       </c>
-      <c r="H161" s="21"/>
-      <c r="I161" s="21"/>
-      <c r="J161" s="21"/>
-      <c r="K161" s="21"/>
-      <c r="L161" s="21"/>
-      <c r="M161" s="22">
+      <c r="H161" s="22"/>
+      <c r="I161" s="22"/>
+      <c r="J161" s="22"/>
+      <c r="K161" s="22"/>
+      <c r="L161" s="22"/>
+      <c r="M161" s="23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -11071,7 +11074,7 @@
       <c r="C166" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="D166" s="23"/>
+      <c r="D166" s="24"/>
       <c r="E166" s="12" t="s">
         <v>640</v>
       </c>
@@ -11150,7 +11153,7 @@
       <c r="B168" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="C168" s="24" t="s">
+      <c r="C168" s="25" t="s">
         <v>660</v>
       </c>
       <c r="D168" s="12" t="s">
@@ -17728,571 +17731,571 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="25"/>
-      <c r="B325" s="25"/>
-      <c r="C325" s="25"/>
-      <c r="D325" s="25"/>
-      <c r="E325" s="25"/>
-      <c r="F325" s="25"/>
-      <c r="G325" s="25"/>
-      <c r="H325" s="26"/>
-      <c r="I325" s="26"/>
-      <c r="J325" s="26"/>
-      <c r="K325" s="26"/>
-      <c r="L325" s="26"/>
-      <c r="M325" s="26"/>
+      <c r="A325" s="26"/>
+      <c r="B325" s="26"/>
+      <c r="C325" s="26"/>
+      <c r="D325" s="26"/>
+      <c r="E325" s="26"/>
+      <c r="F325" s="26"/>
+      <c r="G325" s="26"/>
+      <c r="H325" s="27"/>
+      <c r="I325" s="27"/>
+      <c r="J325" s="27"/>
+      <c r="K325" s="27"/>
+      <c r="L325" s="27"/>
+      <c r="M325" s="27"/>
     </row>
     <row r="326">
-      <c r="A326" s="25"/>
-      <c r="B326" s="25"/>
-      <c r="C326" s="25"/>
-      <c r="D326" s="25"/>
-      <c r="E326" s="25"/>
-      <c r="F326" s="25"/>
-      <c r="G326" s="25"/>
-      <c r="H326" s="26"/>
-      <c r="I326" s="26"/>
-      <c r="J326" s="26"/>
-      <c r="K326" s="26"/>
-      <c r="L326" s="26"/>
-      <c r="M326" s="26"/>
+      <c r="A326" s="26"/>
+      <c r="B326" s="26"/>
+      <c r="C326" s="26"/>
+      <c r="D326" s="26"/>
+      <c r="E326" s="26"/>
+      <c r="F326" s="26"/>
+      <c r="G326" s="26"/>
+      <c r="H326" s="27"/>
+      <c r="I326" s="27"/>
+      <c r="J326" s="27"/>
+      <c r="K326" s="27"/>
+      <c r="L326" s="27"/>
+      <c r="M326" s="27"/>
     </row>
     <row r="327">
-      <c r="A327" s="25"/>
-      <c r="B327" s="25"/>
-      <c r="C327" s="25"/>
-      <c r="D327" s="25"/>
-      <c r="E327" s="25"/>
-      <c r="F327" s="25"/>
-      <c r="G327" s="25"/>
-      <c r="H327" s="26"/>
-      <c r="I327" s="26"/>
-      <c r="J327" s="26"/>
-      <c r="K327" s="26"/>
-      <c r="L327" s="26"/>
-      <c r="M327" s="26"/>
+      <c r="A327" s="26"/>
+      <c r="B327" s="26"/>
+      <c r="C327" s="26"/>
+      <c r="D327" s="26"/>
+      <c r="E327" s="26"/>
+      <c r="F327" s="26"/>
+      <c r="G327" s="26"/>
+      <c r="H327" s="27"/>
+      <c r="I327" s="27"/>
+      <c r="J327" s="27"/>
+      <c r="K327" s="27"/>
+      <c r="L327" s="27"/>
+      <c r="M327" s="27"/>
     </row>
     <row r="328">
-      <c r="A328" s="25"/>
-      <c r="B328" s="25"/>
-      <c r="C328" s="25"/>
-      <c r="D328" s="25"/>
-      <c r="E328" s="25"/>
-      <c r="F328" s="25"/>
-      <c r="G328" s="25"/>
-      <c r="H328" s="26"/>
-      <c r="I328" s="26"/>
-      <c r="J328" s="26"/>
-      <c r="K328" s="26"/>
-      <c r="L328" s="26"/>
-      <c r="M328" s="26"/>
+      <c r="A328" s="26"/>
+      <c r="B328" s="26"/>
+      <c r="C328" s="26"/>
+      <c r="D328" s="26"/>
+      <c r="E328" s="26"/>
+      <c r="F328" s="26"/>
+      <c r="G328" s="26"/>
+      <c r="H328" s="27"/>
+      <c r="I328" s="27"/>
+      <c r="J328" s="27"/>
+      <c r="K328" s="27"/>
+      <c r="L328" s="27"/>
+      <c r="M328" s="27"/>
     </row>
     <row r="329">
-      <c r="A329" s="25"/>
-      <c r="B329" s="25"/>
-      <c r="C329" s="25"/>
-      <c r="D329" s="25"/>
-      <c r="E329" s="25"/>
-      <c r="F329" s="25"/>
-      <c r="G329" s="25"/>
-      <c r="H329" s="26"/>
-      <c r="I329" s="26"/>
-      <c r="J329" s="26"/>
-      <c r="K329" s="26"/>
-      <c r="L329" s="26"/>
-      <c r="M329" s="26"/>
+      <c r="A329" s="26"/>
+      <c r="B329" s="26"/>
+      <c r="C329" s="26"/>
+      <c r="D329" s="26"/>
+      <c r="E329" s="26"/>
+      <c r="F329" s="26"/>
+      <c r="G329" s="26"/>
+      <c r="H329" s="27"/>
+      <c r="I329" s="27"/>
+      <c r="J329" s="27"/>
+      <c r="K329" s="27"/>
+      <c r="L329" s="27"/>
+      <c r="M329" s="27"/>
     </row>
     <row r="330">
-      <c r="A330" s="25"/>
-      <c r="B330" s="25"/>
-      <c r="C330" s="25"/>
-      <c r="D330" s="25"/>
-      <c r="E330" s="25"/>
-      <c r="F330" s="25"/>
-      <c r="G330" s="25"/>
-      <c r="H330" s="26"/>
-      <c r="I330" s="26"/>
-      <c r="J330" s="26"/>
-      <c r="K330" s="26"/>
-      <c r="L330" s="26"/>
-      <c r="M330" s="26"/>
+      <c r="A330" s="26"/>
+      <c r="B330" s="26"/>
+      <c r="C330" s="26"/>
+      <c r="D330" s="26"/>
+      <c r="E330" s="26"/>
+      <c r="F330" s="26"/>
+      <c r="G330" s="26"/>
+      <c r="H330" s="27"/>
+      <c r="I330" s="27"/>
+      <c r="J330" s="27"/>
+      <c r="K330" s="27"/>
+      <c r="L330" s="27"/>
+      <c r="M330" s="27"/>
     </row>
     <row r="331">
-      <c r="A331" s="25"/>
-      <c r="B331" s="25"/>
-      <c r="C331" s="25"/>
-      <c r="D331" s="25"/>
-      <c r="E331" s="25"/>
-      <c r="F331" s="25"/>
-      <c r="G331" s="25"/>
-      <c r="H331" s="26"/>
-      <c r="I331" s="26"/>
-      <c r="J331" s="26"/>
-      <c r="K331" s="26"/>
-      <c r="L331" s="26"/>
-      <c r="M331" s="26"/>
+      <c r="A331" s="26"/>
+      <c r="B331" s="26"/>
+      <c r="C331" s="26"/>
+      <c r="D331" s="26"/>
+      <c r="E331" s="26"/>
+      <c r="F331" s="26"/>
+      <c r="G331" s="26"/>
+      <c r="H331" s="27"/>
+      <c r="I331" s="27"/>
+      <c r="J331" s="27"/>
+      <c r="K331" s="27"/>
+      <c r="L331" s="27"/>
+      <c r="M331" s="27"/>
     </row>
     <row r="332">
-      <c r="A332" s="25"/>
-      <c r="B332" s="25"/>
-      <c r="C332" s="25"/>
-      <c r="D332" s="25"/>
-      <c r="E332" s="25"/>
-      <c r="F332" s="25"/>
-      <c r="G332" s="25"/>
-      <c r="H332" s="26"/>
-      <c r="I332" s="26"/>
-      <c r="J332" s="26"/>
-      <c r="K332" s="26"/>
-      <c r="L332" s="26"/>
-      <c r="M332" s="26"/>
+      <c r="A332" s="26"/>
+      <c r="B332" s="26"/>
+      <c r="C332" s="26"/>
+      <c r="D332" s="26"/>
+      <c r="E332" s="26"/>
+      <c r="F332" s="26"/>
+      <c r="G332" s="26"/>
+      <c r="H332" s="27"/>
+      <c r="I332" s="27"/>
+      <c r="J332" s="27"/>
+      <c r="K332" s="27"/>
+      <c r="L332" s="27"/>
+      <c r="M332" s="27"/>
     </row>
     <row r="333">
-      <c r="A333" s="25"/>
-      <c r="B333" s="25"/>
-      <c r="C333" s="25"/>
-      <c r="D333" s="25"/>
-      <c r="E333" s="25"/>
-      <c r="F333" s="25"/>
-      <c r="G333" s="25"/>
-      <c r="H333" s="26"/>
-      <c r="I333" s="26"/>
-      <c r="J333" s="26"/>
-      <c r="K333" s="26"/>
-      <c r="L333" s="26"/>
-      <c r="M333" s="26"/>
+      <c r="A333" s="26"/>
+      <c r="B333" s="26"/>
+      <c r="C333" s="26"/>
+      <c r="D333" s="26"/>
+      <c r="E333" s="26"/>
+      <c r="F333" s="26"/>
+      <c r="G333" s="26"/>
+      <c r="H333" s="27"/>
+      <c r="I333" s="27"/>
+      <c r="J333" s="27"/>
+      <c r="K333" s="27"/>
+      <c r="L333" s="27"/>
+      <c r="M333" s="27"/>
     </row>
     <row r="334">
-      <c r="A334" s="25"/>
-      <c r="B334" s="25"/>
-      <c r="C334" s="25"/>
-      <c r="D334" s="25"/>
-      <c r="E334" s="25"/>
-      <c r="F334" s="25"/>
-      <c r="G334" s="25"/>
-      <c r="H334" s="26"/>
-      <c r="I334" s="26"/>
-      <c r="J334" s="26"/>
-      <c r="K334" s="26"/>
-      <c r="L334" s="26"/>
-      <c r="M334" s="26"/>
+      <c r="A334" s="26"/>
+      <c r="B334" s="26"/>
+      <c r="C334" s="26"/>
+      <c r="D334" s="26"/>
+      <c r="E334" s="26"/>
+      <c r="F334" s="26"/>
+      <c r="G334" s="26"/>
+      <c r="H334" s="27"/>
+      <c r="I334" s="27"/>
+      <c r="J334" s="27"/>
+      <c r="K334" s="27"/>
+      <c r="L334" s="27"/>
+      <c r="M334" s="27"/>
     </row>
     <row r="335">
-      <c r="A335" s="25"/>
-      <c r="B335" s="25"/>
-      <c r="C335" s="25"/>
-      <c r="D335" s="25"/>
-      <c r="E335" s="25"/>
-      <c r="F335" s="25"/>
-      <c r="G335" s="25"/>
-      <c r="H335" s="26"/>
-      <c r="I335" s="26"/>
-      <c r="J335" s="26"/>
-      <c r="K335" s="26"/>
-      <c r="L335" s="26"/>
-      <c r="M335" s="26"/>
+      <c r="A335" s="26"/>
+      <c r="B335" s="26"/>
+      <c r="C335" s="26"/>
+      <c r="D335" s="26"/>
+      <c r="E335" s="26"/>
+      <c r="F335" s="26"/>
+      <c r="G335" s="26"/>
+      <c r="H335" s="27"/>
+      <c r="I335" s="27"/>
+      <c r="J335" s="27"/>
+      <c r="K335" s="27"/>
+      <c r="L335" s="27"/>
+      <c r="M335" s="27"/>
     </row>
     <row r="336">
-      <c r="A336" s="25"/>
-      <c r="B336" s="25"/>
-      <c r="C336" s="25"/>
-      <c r="D336" s="25"/>
-      <c r="E336" s="25"/>
-      <c r="F336" s="25"/>
-      <c r="G336" s="25"/>
-      <c r="H336" s="26"/>
-      <c r="I336" s="26"/>
-      <c r="J336" s="26"/>
-      <c r="K336" s="26"/>
-      <c r="L336" s="26"/>
-      <c r="M336" s="26"/>
+      <c r="A336" s="26"/>
+      <c r="B336" s="26"/>
+      <c r="C336" s="26"/>
+      <c r="D336" s="26"/>
+      <c r="E336" s="26"/>
+      <c r="F336" s="26"/>
+      <c r="G336" s="26"/>
+      <c r="H336" s="27"/>
+      <c r="I336" s="27"/>
+      <c r="J336" s="27"/>
+      <c r="K336" s="27"/>
+      <c r="L336" s="27"/>
+      <c r="M336" s="27"/>
     </row>
     <row r="337">
-      <c r="A337" s="25"/>
-      <c r="B337" s="25"/>
-      <c r="C337" s="25"/>
-      <c r="D337" s="25"/>
-      <c r="E337" s="25"/>
-      <c r="F337" s="25"/>
-      <c r="G337" s="25"/>
-      <c r="H337" s="26"/>
-      <c r="I337" s="26"/>
-      <c r="J337" s="26"/>
-      <c r="K337" s="26"/>
-      <c r="L337" s="26"/>
-      <c r="M337" s="26"/>
+      <c r="A337" s="26"/>
+      <c r="B337" s="26"/>
+      <c r="C337" s="26"/>
+      <c r="D337" s="26"/>
+      <c r="E337" s="26"/>
+      <c r="F337" s="26"/>
+      <c r="G337" s="26"/>
+      <c r="H337" s="27"/>
+      <c r="I337" s="27"/>
+      <c r="J337" s="27"/>
+      <c r="K337" s="27"/>
+      <c r="L337" s="27"/>
+      <c r="M337" s="27"/>
     </row>
     <row r="338">
-      <c r="A338" s="25"/>
-      <c r="B338" s="25"/>
-      <c r="C338" s="25"/>
-      <c r="D338" s="25"/>
-      <c r="E338" s="25"/>
-      <c r="F338" s="25"/>
-      <c r="G338" s="25"/>
-      <c r="H338" s="26"/>
-      <c r="I338" s="26"/>
-      <c r="J338" s="26"/>
-      <c r="K338" s="26"/>
-      <c r="L338" s="26"/>
-      <c r="M338" s="26"/>
+      <c r="A338" s="26"/>
+      <c r="B338" s="26"/>
+      <c r="C338" s="26"/>
+      <c r="D338" s="26"/>
+      <c r="E338" s="26"/>
+      <c r="F338" s="26"/>
+      <c r="G338" s="26"/>
+      <c r="H338" s="27"/>
+      <c r="I338" s="27"/>
+      <c r="J338" s="27"/>
+      <c r="K338" s="27"/>
+      <c r="L338" s="27"/>
+      <c r="M338" s="27"/>
     </row>
     <row r="339">
-      <c r="A339" s="25"/>
-      <c r="B339" s="25"/>
-      <c r="C339" s="25"/>
-      <c r="D339" s="25"/>
-      <c r="E339" s="25"/>
-      <c r="F339" s="25"/>
-      <c r="G339" s="25"/>
-      <c r="H339" s="26"/>
-      <c r="I339" s="26"/>
-      <c r="J339" s="26"/>
-      <c r="K339" s="26"/>
-      <c r="L339" s="26"/>
-      <c r="M339" s="26"/>
+      <c r="A339" s="26"/>
+      <c r="B339" s="26"/>
+      <c r="C339" s="26"/>
+      <c r="D339" s="26"/>
+      <c r="E339" s="26"/>
+      <c r="F339" s="26"/>
+      <c r="G339" s="26"/>
+      <c r="H339" s="27"/>
+      <c r="I339" s="27"/>
+      <c r="J339" s="27"/>
+      <c r="K339" s="27"/>
+      <c r="L339" s="27"/>
+      <c r="M339" s="27"/>
     </row>
     <row r="340">
-      <c r="A340" s="25"/>
-      <c r="B340" s="25"/>
-      <c r="C340" s="25"/>
-      <c r="D340" s="25"/>
-      <c r="E340" s="25"/>
-      <c r="F340" s="25"/>
-      <c r="G340" s="25"/>
-      <c r="H340" s="26"/>
-      <c r="I340" s="26"/>
-      <c r="J340" s="26"/>
-      <c r="K340" s="26"/>
-      <c r="L340" s="26"/>
-      <c r="M340" s="26"/>
+      <c r="A340" s="26"/>
+      <c r="B340" s="26"/>
+      <c r="C340" s="26"/>
+      <c r="D340" s="26"/>
+      <c r="E340" s="26"/>
+      <c r="F340" s="26"/>
+      <c r="G340" s="26"/>
+      <c r="H340" s="27"/>
+      <c r="I340" s="27"/>
+      <c r="J340" s="27"/>
+      <c r="K340" s="27"/>
+      <c r="L340" s="27"/>
+      <c r="M340" s="27"/>
     </row>
     <row r="341">
-      <c r="A341" s="25"/>
-      <c r="B341" s="25"/>
-      <c r="C341" s="25"/>
-      <c r="D341" s="25"/>
-      <c r="E341" s="25"/>
-      <c r="F341" s="25"/>
-      <c r="G341" s="25"/>
-      <c r="H341" s="26"/>
-      <c r="I341" s="26"/>
-      <c r="J341" s="26"/>
-      <c r="K341" s="26"/>
-      <c r="L341" s="26"/>
-      <c r="M341" s="26"/>
+      <c r="A341" s="26"/>
+      <c r="B341" s="26"/>
+      <c r="C341" s="26"/>
+      <c r="D341" s="26"/>
+      <c r="E341" s="26"/>
+      <c r="F341" s="26"/>
+      <c r="G341" s="26"/>
+      <c r="H341" s="27"/>
+      <c r="I341" s="27"/>
+      <c r="J341" s="27"/>
+      <c r="K341" s="27"/>
+      <c r="L341" s="27"/>
+      <c r="M341" s="27"/>
     </row>
     <row r="342">
-      <c r="A342" s="25"/>
-      <c r="B342" s="25"/>
-      <c r="C342" s="25"/>
-      <c r="D342" s="25"/>
-      <c r="E342" s="25"/>
-      <c r="F342" s="25"/>
-      <c r="G342" s="25"/>
-      <c r="H342" s="26"/>
-      <c r="I342" s="26"/>
-      <c r="J342" s="26"/>
-      <c r="K342" s="26"/>
-      <c r="L342" s="26"/>
-      <c r="M342" s="26"/>
+      <c r="A342" s="26"/>
+      <c r="B342" s="26"/>
+      <c r="C342" s="26"/>
+      <c r="D342" s="26"/>
+      <c r="E342" s="26"/>
+      <c r="F342" s="26"/>
+      <c r="G342" s="26"/>
+      <c r="H342" s="27"/>
+      <c r="I342" s="27"/>
+      <c r="J342" s="27"/>
+      <c r="K342" s="27"/>
+      <c r="L342" s="27"/>
+      <c r="M342" s="27"/>
     </row>
     <row r="343">
-      <c r="A343" s="25"/>
-      <c r="B343" s="25"/>
-      <c r="C343" s="25"/>
-      <c r="D343" s="25"/>
-      <c r="E343" s="25"/>
-      <c r="F343" s="25"/>
-      <c r="G343" s="25"/>
-      <c r="H343" s="26"/>
-      <c r="I343" s="26"/>
-      <c r="J343" s="26"/>
-      <c r="K343" s="26"/>
-      <c r="L343" s="26"/>
-      <c r="M343" s="26"/>
+      <c r="A343" s="26"/>
+      <c r="B343" s="26"/>
+      <c r="C343" s="26"/>
+      <c r="D343" s="26"/>
+      <c r="E343" s="26"/>
+      <c r="F343" s="26"/>
+      <c r="G343" s="26"/>
+      <c r="H343" s="27"/>
+      <c r="I343" s="27"/>
+      <c r="J343" s="27"/>
+      <c r="K343" s="27"/>
+      <c r="L343" s="27"/>
+      <c r="M343" s="27"/>
     </row>
     <row r="344">
-      <c r="A344" s="25"/>
-      <c r="B344" s="25"/>
-      <c r="C344" s="25"/>
-      <c r="D344" s="25"/>
-      <c r="E344" s="25"/>
-      <c r="F344" s="25"/>
-      <c r="G344" s="25"/>
-      <c r="H344" s="26"/>
-      <c r="I344" s="26"/>
-      <c r="J344" s="26"/>
-      <c r="K344" s="26"/>
-      <c r="L344" s="26"/>
-      <c r="M344" s="26"/>
+      <c r="A344" s="26"/>
+      <c r="B344" s="26"/>
+      <c r="C344" s="26"/>
+      <c r="D344" s="26"/>
+      <c r="E344" s="26"/>
+      <c r="F344" s="26"/>
+      <c r="G344" s="26"/>
+      <c r="H344" s="27"/>
+      <c r="I344" s="27"/>
+      <c r="J344" s="27"/>
+      <c r="K344" s="27"/>
+      <c r="L344" s="27"/>
+      <c r="M344" s="27"/>
     </row>
     <row r="345">
-      <c r="A345" s="25"/>
-      <c r="B345" s="25"/>
-      <c r="C345" s="25"/>
-      <c r="D345" s="25"/>
-      <c r="E345" s="25"/>
-      <c r="F345" s="25"/>
-      <c r="G345" s="25"/>
-      <c r="H345" s="26"/>
-      <c r="I345" s="26"/>
-      <c r="J345" s="26"/>
-      <c r="K345" s="26"/>
-      <c r="L345" s="26"/>
-      <c r="M345" s="26"/>
+      <c r="A345" s="26"/>
+      <c r="B345" s="26"/>
+      <c r="C345" s="26"/>
+      <c r="D345" s="26"/>
+      <c r="E345" s="26"/>
+      <c r="F345" s="26"/>
+      <c r="G345" s="26"/>
+      <c r="H345" s="27"/>
+      <c r="I345" s="27"/>
+      <c r="J345" s="27"/>
+      <c r="K345" s="27"/>
+      <c r="L345" s="27"/>
+      <c r="M345" s="27"/>
     </row>
     <row r="346">
-      <c r="A346" s="25"/>
-      <c r="B346" s="25"/>
-      <c r="C346" s="25"/>
-      <c r="D346" s="25"/>
-      <c r="E346" s="25"/>
-      <c r="F346" s="25"/>
-      <c r="G346" s="25"/>
-      <c r="H346" s="26"/>
-      <c r="I346" s="26"/>
-      <c r="J346" s="26"/>
-      <c r="K346" s="26"/>
-      <c r="L346" s="26"/>
-      <c r="M346" s="26"/>
+      <c r="A346" s="26"/>
+      <c r="B346" s="26"/>
+      <c r="C346" s="26"/>
+      <c r="D346" s="26"/>
+      <c r="E346" s="26"/>
+      <c r="F346" s="26"/>
+      <c r="G346" s="26"/>
+      <c r="H346" s="27"/>
+      <c r="I346" s="27"/>
+      <c r="J346" s="27"/>
+      <c r="K346" s="27"/>
+      <c r="L346" s="27"/>
+      <c r="M346" s="27"/>
     </row>
     <row r="347">
-      <c r="A347" s="25"/>
-      <c r="B347" s="25"/>
-      <c r="C347" s="25"/>
-      <c r="D347" s="25"/>
-      <c r="E347" s="25"/>
-      <c r="F347" s="25"/>
-      <c r="G347" s="25"/>
-      <c r="H347" s="26"/>
-      <c r="I347" s="26"/>
-      <c r="J347" s="26"/>
-      <c r="K347" s="26"/>
-      <c r="L347" s="26"/>
-      <c r="M347" s="26"/>
+      <c r="A347" s="26"/>
+      <c r="B347" s="26"/>
+      <c r="C347" s="26"/>
+      <c r="D347" s="26"/>
+      <c r="E347" s="26"/>
+      <c r="F347" s="26"/>
+      <c r="G347" s="26"/>
+      <c r="H347" s="27"/>
+      <c r="I347" s="27"/>
+      <c r="J347" s="27"/>
+      <c r="K347" s="27"/>
+      <c r="L347" s="27"/>
+      <c r="M347" s="27"/>
     </row>
     <row r="348">
-      <c r="A348" s="25"/>
-      <c r="B348" s="25"/>
-      <c r="C348" s="25"/>
-      <c r="D348" s="25"/>
-      <c r="E348" s="25"/>
-      <c r="F348" s="25"/>
-      <c r="G348" s="25"/>
-      <c r="H348" s="26"/>
-      <c r="I348" s="26"/>
-      <c r="J348" s="26"/>
-      <c r="K348" s="26"/>
-      <c r="L348" s="26"/>
-      <c r="M348" s="26"/>
+      <c r="A348" s="26"/>
+      <c r="B348" s="26"/>
+      <c r="C348" s="26"/>
+      <c r="D348" s="26"/>
+      <c r="E348" s="26"/>
+      <c r="F348" s="26"/>
+      <c r="G348" s="26"/>
+      <c r="H348" s="27"/>
+      <c r="I348" s="27"/>
+      <c r="J348" s="27"/>
+      <c r="K348" s="27"/>
+      <c r="L348" s="27"/>
+      <c r="M348" s="27"/>
     </row>
     <row r="349">
-      <c r="A349" s="25"/>
-      <c r="B349" s="25"/>
-      <c r="C349" s="25"/>
-      <c r="D349" s="25"/>
-      <c r="E349" s="25"/>
-      <c r="F349" s="25"/>
-      <c r="G349" s="25"/>
-      <c r="H349" s="26"/>
-      <c r="I349" s="26"/>
-      <c r="J349" s="26"/>
-      <c r="K349" s="26"/>
-      <c r="L349" s="26"/>
-      <c r="M349" s="26"/>
+      <c r="A349" s="26"/>
+      <c r="B349" s="26"/>
+      <c r="C349" s="26"/>
+      <c r="D349" s="26"/>
+      <c r="E349" s="26"/>
+      <c r="F349" s="26"/>
+      <c r="G349" s="26"/>
+      <c r="H349" s="27"/>
+      <c r="I349" s="27"/>
+      <c r="J349" s="27"/>
+      <c r="K349" s="27"/>
+      <c r="L349" s="27"/>
+      <c r="M349" s="27"/>
     </row>
     <row r="350">
-      <c r="A350" s="25"/>
-      <c r="B350" s="25"/>
-      <c r="C350" s="25"/>
-      <c r="D350" s="25"/>
-      <c r="E350" s="25"/>
-      <c r="F350" s="25"/>
-      <c r="G350" s="25"/>
-      <c r="H350" s="26"/>
-      <c r="I350" s="26"/>
-      <c r="J350" s="26"/>
-      <c r="K350" s="26"/>
-      <c r="L350" s="26"/>
-      <c r="M350" s="26"/>
+      <c r="A350" s="26"/>
+      <c r="B350" s="26"/>
+      <c r="C350" s="26"/>
+      <c r="D350" s="26"/>
+      <c r="E350" s="26"/>
+      <c r="F350" s="26"/>
+      <c r="G350" s="26"/>
+      <c r="H350" s="27"/>
+      <c r="I350" s="27"/>
+      <c r="J350" s="27"/>
+      <c r="K350" s="27"/>
+      <c r="L350" s="27"/>
+      <c r="M350" s="27"/>
     </row>
     <row r="351">
-      <c r="A351" s="25"/>
-      <c r="B351" s="25"/>
-      <c r="C351" s="25"/>
-      <c r="D351" s="25"/>
-      <c r="E351" s="25"/>
-      <c r="F351" s="25"/>
-      <c r="G351" s="25"/>
-      <c r="H351" s="26"/>
-      <c r="I351" s="26"/>
-      <c r="J351" s="26"/>
-      <c r="K351" s="26"/>
-      <c r="L351" s="26"/>
-      <c r="M351" s="26"/>
+      <c r="A351" s="26"/>
+      <c r="B351" s="26"/>
+      <c r="C351" s="26"/>
+      <c r="D351" s="26"/>
+      <c r="E351" s="26"/>
+      <c r="F351" s="26"/>
+      <c r="G351" s="26"/>
+      <c r="H351" s="27"/>
+      <c r="I351" s="27"/>
+      <c r="J351" s="27"/>
+      <c r="K351" s="27"/>
+      <c r="L351" s="27"/>
+      <c r="M351" s="27"/>
     </row>
     <row r="352">
-      <c r="A352" s="25"/>
-      <c r="B352" s="25"/>
-      <c r="C352" s="25"/>
-      <c r="D352" s="25"/>
-      <c r="E352" s="25"/>
-      <c r="F352" s="25"/>
-      <c r="G352" s="25"/>
-      <c r="H352" s="26"/>
-      <c r="I352" s="26"/>
-      <c r="J352" s="26"/>
-      <c r="K352" s="26"/>
-      <c r="L352" s="26"/>
-      <c r="M352" s="26"/>
+      <c r="A352" s="26"/>
+      <c r="B352" s="26"/>
+      <c r="C352" s="26"/>
+      <c r="D352" s="26"/>
+      <c r="E352" s="26"/>
+      <c r="F352" s="26"/>
+      <c r="G352" s="26"/>
+      <c r="H352" s="27"/>
+      <c r="I352" s="27"/>
+      <c r="J352" s="27"/>
+      <c r="K352" s="27"/>
+      <c r="L352" s="27"/>
+      <c r="M352" s="27"/>
     </row>
     <row r="353">
-      <c r="A353" s="25"/>
-      <c r="B353" s="25"/>
-      <c r="C353" s="25"/>
-      <c r="D353" s="25"/>
-      <c r="E353" s="25"/>
-      <c r="F353" s="25"/>
-      <c r="G353" s="25"/>
-      <c r="H353" s="26"/>
-      <c r="I353" s="26"/>
-      <c r="J353" s="26"/>
-      <c r="K353" s="26"/>
-      <c r="L353" s="26"/>
-      <c r="M353" s="26"/>
+      <c r="A353" s="26"/>
+      <c r="B353" s="26"/>
+      <c r="C353" s="26"/>
+      <c r="D353" s="26"/>
+      <c r="E353" s="26"/>
+      <c r="F353" s="26"/>
+      <c r="G353" s="26"/>
+      <c r="H353" s="27"/>
+      <c r="I353" s="27"/>
+      <c r="J353" s="27"/>
+      <c r="K353" s="27"/>
+      <c r="L353" s="27"/>
+      <c r="M353" s="27"/>
     </row>
     <row r="354">
-      <c r="A354" s="25"/>
-      <c r="B354" s="25"/>
-      <c r="C354" s="25"/>
-      <c r="D354" s="25"/>
-      <c r="E354" s="25"/>
-      <c r="F354" s="25"/>
-      <c r="G354" s="25"/>
-      <c r="H354" s="26"/>
-      <c r="I354" s="26"/>
-      <c r="J354" s="26"/>
-      <c r="K354" s="26"/>
-      <c r="L354" s="26"/>
-      <c r="M354" s="26"/>
+      <c r="A354" s="26"/>
+      <c r="B354" s="26"/>
+      <c r="C354" s="26"/>
+      <c r="D354" s="26"/>
+      <c r="E354" s="26"/>
+      <c r="F354" s="26"/>
+      <c r="G354" s="26"/>
+      <c r="H354" s="27"/>
+      <c r="I354" s="27"/>
+      <c r="J354" s="27"/>
+      <c r="K354" s="27"/>
+      <c r="L354" s="27"/>
+      <c r="M354" s="27"/>
     </row>
     <row r="355">
-      <c r="A355" s="25"/>
-      <c r="B355" s="25"/>
-      <c r="C355" s="25"/>
-      <c r="D355" s="25"/>
-      <c r="E355" s="25"/>
-      <c r="F355" s="25"/>
-      <c r="G355" s="25"/>
-      <c r="H355" s="26"/>
-      <c r="I355" s="26"/>
-      <c r="J355" s="26"/>
-      <c r="K355" s="26"/>
-      <c r="L355" s="26"/>
-      <c r="M355" s="26"/>
+      <c r="A355" s="26"/>
+      <c r="B355" s="26"/>
+      <c r="C355" s="26"/>
+      <c r="D355" s="26"/>
+      <c r="E355" s="26"/>
+      <c r="F355" s="26"/>
+      <c r="G355" s="26"/>
+      <c r="H355" s="27"/>
+      <c r="I355" s="27"/>
+      <c r="J355" s="27"/>
+      <c r="K355" s="27"/>
+      <c r="L355" s="27"/>
+      <c r="M355" s="27"/>
     </row>
     <row r="356">
-      <c r="A356" s="25"/>
-      <c r="B356" s="25"/>
-      <c r="C356" s="25"/>
-      <c r="D356" s="25"/>
-      <c r="E356" s="25"/>
-      <c r="F356" s="25"/>
-      <c r="G356" s="25"/>
-      <c r="H356" s="26"/>
-      <c r="I356" s="26"/>
-      <c r="J356" s="26"/>
-      <c r="K356" s="26"/>
-      <c r="L356" s="26"/>
-      <c r="M356" s="26"/>
+      <c r="A356" s="26"/>
+      <c r="B356" s="26"/>
+      <c r="C356" s="26"/>
+      <c r="D356" s="26"/>
+      <c r="E356" s="26"/>
+      <c r="F356" s="26"/>
+      <c r="G356" s="26"/>
+      <c r="H356" s="27"/>
+      <c r="I356" s="27"/>
+      <c r="J356" s="27"/>
+      <c r="K356" s="27"/>
+      <c r="L356" s="27"/>
+      <c r="M356" s="27"/>
     </row>
     <row r="357">
-      <c r="A357" s="25"/>
-      <c r="B357" s="25"/>
-      <c r="C357" s="25"/>
-      <c r="D357" s="25"/>
-      <c r="E357" s="25"/>
-      <c r="F357" s="25"/>
-      <c r="G357" s="25"/>
-      <c r="H357" s="26"/>
-      <c r="I357" s="26"/>
-      <c r="J357" s="26"/>
-      <c r="K357" s="26"/>
-      <c r="L357" s="26"/>
-      <c r="M357" s="26"/>
+      <c r="A357" s="26"/>
+      <c r="B357" s="26"/>
+      <c r="C357" s="26"/>
+      <c r="D357" s="26"/>
+      <c r="E357" s="26"/>
+      <c r="F357" s="26"/>
+      <c r="G357" s="26"/>
+      <c r="H357" s="27"/>
+      <c r="I357" s="27"/>
+      <c r="J357" s="27"/>
+      <c r="K357" s="27"/>
+      <c r="L357" s="27"/>
+      <c r="M357" s="27"/>
     </row>
     <row r="358">
-      <c r="A358" s="25"/>
-      <c r="B358" s="25"/>
-      <c r="C358" s="25"/>
-      <c r="D358" s="25"/>
-      <c r="E358" s="25"/>
-      <c r="F358" s="25"/>
-      <c r="G358" s="25"/>
-      <c r="H358" s="26"/>
-      <c r="I358" s="26"/>
-      <c r="J358" s="26"/>
-      <c r="K358" s="26"/>
-      <c r="L358" s="26"/>
-      <c r="M358" s="26"/>
+      <c r="A358" s="26"/>
+      <c r="B358" s="26"/>
+      <c r="C358" s="26"/>
+      <c r="D358" s="26"/>
+      <c r="E358" s="26"/>
+      <c r="F358" s="26"/>
+      <c r="G358" s="26"/>
+      <c r="H358" s="27"/>
+      <c r="I358" s="27"/>
+      <c r="J358" s="27"/>
+      <c r="K358" s="27"/>
+      <c r="L358" s="27"/>
+      <c r="M358" s="27"/>
     </row>
     <row r="359">
-      <c r="A359" s="25"/>
-      <c r="B359" s="25"/>
-      <c r="C359" s="25"/>
-      <c r="D359" s="25"/>
-      <c r="E359" s="25"/>
-      <c r="F359" s="25"/>
-      <c r="G359" s="25"/>
-      <c r="H359" s="26"/>
-      <c r="I359" s="26"/>
-      <c r="J359" s="26"/>
-      <c r="K359" s="26"/>
-      <c r="L359" s="26"/>
-      <c r="M359" s="26"/>
+      <c r="A359" s="26"/>
+      <c r="B359" s="26"/>
+      <c r="C359" s="26"/>
+      <c r="D359" s="26"/>
+      <c r="E359" s="26"/>
+      <c r="F359" s="26"/>
+      <c r="G359" s="26"/>
+      <c r="H359" s="27"/>
+      <c r="I359" s="27"/>
+      <c r="J359" s="27"/>
+      <c r="K359" s="27"/>
+      <c r="L359" s="27"/>
+      <c r="M359" s="27"/>
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{6CFFF1F8-EEAD-47B1-A5BA-9B98655A952B}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{98289A86-091A-432E-95EB-62C0CCB6E499}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{42D6E9FA-5371-4DCF-B97C-438E291F0C15}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{1DF0D9CB-1060-4CA2-8949-B31DCBD5B4BF}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{1B3A8ACD-D417-4637-A685-81D9381FF1DE}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{55AED9A0-DA0D-4128-B5D2-1BF8D79ECD96}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{E19D6905-7219-4716-8E35-399AC7C1BC00}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{018C47CD-611C-4A4D-9F70-D959A33B0A04}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{ECF78DD8-3C13-45CB-A702-9BDF29315AF0}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{113A483A-B910-44BD-9A0A-C77FF7CF5327}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{6EA19BB9-567C-4055-96CB-2C19019C8916}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{D4852FD5-0F09-401B-B4EA-0D373D545BD2}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{8AACF8F8-B55E-4915-9F46-991C008EBE09}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{04333B8C-AC3F-4D65-9552-CFEC1FEC2F88}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{1EA62444-B123-4C0B-8F7F-3B200448A206}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{7E949F86-CBBE-4D4A-B11E-3032717324AC}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
-    <customSheetView guid="{B42CC50D-F60F-42F9-B8C0-FC77153034DE}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{00AEBA2B-1B46-4428-9543-9DBC253D4359}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29">
         <sortState ref="A1:M29">
           <sortCondition ref="F1:F29"/>
         </sortState>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{D6D6AAF0-767B-47ED-B3D3-B6430EEAFC24}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{9EF01319-1434-4553-ABA9-8A8DB3118517}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29">
         <sortState ref="A1:M29">
           <sortCondition ref="G1:G29"/>
         </sortState>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{BDCCA16F-5B03-4638-AFE1-84255B44CB7F}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{7DCAD69D-5D4D-42D8-AF66-6922AFF61F41}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$M$29"/>
     </customSheetView>
   </customSheetViews>
